--- a/docs/0.6_Issuer_sales_report.xlsx
+++ b/docs/0.6_Issuer_sales_report.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ridango-my.sharepoint.com/personal/margaritta_erikson_ridango_com/Documents/Isiklik/Koolitusmaterjalid/ValiIT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\IdeaProjects\etas\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{52569610-7D2F-41CC-98C0-C5E79BBE3713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4045B792-243D-41CB-A4BF-000C9C33DEB2}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4045B792-243D-41CB-A4BF-000C9C33DEB2}"/>
   </bookViews>
   <sheets>
     <sheet name="Leht1" sheetId="1" r:id="rId1"/>
